--- a/artfynd/A 63717-2023 artfynd.xlsx
+++ b/artfynd/A 63717-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119825772</v>
+        <v>119825809</v>
       </c>
       <c r="B2" t="n">
-        <v>90907</v>
+        <v>74643</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2063</v>
+        <v>1467</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119825814</v>
+        <v>119825772</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
+        <v>90907</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>2063</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119825809</v>
+        <v>119825814</v>
       </c>
       <c r="B4" t="n">
-        <v>74643</v>
+        <v>90580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1467</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>

--- a/artfynd/A 63717-2023 artfynd.xlsx
+++ b/artfynd/A 63717-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119825809</v>
+        <v>119825772</v>
       </c>
       <c r="B2" t="n">
-        <v>74643</v>
+        <v>90907</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1467</v>
+        <v>2063</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119825772</v>
+        <v>119825809</v>
       </c>
       <c r="B3" t="n">
-        <v>90907</v>
+        <v>74643</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2063</v>
+        <v>1467</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>

--- a/artfynd/A 63717-2023 artfynd.xlsx
+++ b/artfynd/A 63717-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119825772</v>
+        <v>119825814</v>
       </c>
       <c r="B2" t="n">
-        <v>90907</v>
+        <v>90580</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2063</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119825814</v>
+        <v>119825772</v>
       </c>
       <c r="B4" t="n">
-        <v>90580</v>
+        <v>90907</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>2063</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>

--- a/artfynd/A 63717-2023 artfynd.xlsx
+++ b/artfynd/A 63717-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119825814</v>
       </c>
       <c r="B2" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119825809</v>
+        <v>119825772</v>
       </c>
       <c r="B3" t="n">
-        <v>74643</v>
+        <v>90925</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1467</v>
+        <v>2063</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119825772</v>
+        <v>119825809</v>
       </c>
       <c r="B4" t="n">
-        <v>90907</v>
+        <v>74659</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2063</v>
+        <v>1467</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>

--- a/artfynd/A 63717-2023 artfynd.xlsx
+++ b/artfynd/A 63717-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119825814</v>
+        <v>119825809</v>
       </c>
       <c r="B2" t="n">
-        <v>90598</v>
+        <v>74659</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119825772</v>
+        <v>119825814</v>
       </c>
       <c r="B3" t="n">
-        <v>90925</v>
+        <v>90598</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2063</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119825809</v>
+        <v>119825772</v>
       </c>
       <c r="B4" t="n">
-        <v>74659</v>
+        <v>90925</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1467</v>
+        <v>2063</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
